--- a/rtss-pre1917/src/main/resources/ugvi/year-volumes/new/1888-new.xlsx
+++ b/rtss-pre1917/src/main/resources/ugvi/year-volumes/new/1888-new.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\ugvi\year-volumes\new\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D39B6C05-42B0-470B-AFAC-34F8F9D41D8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{464B532B-9910-4F1C-A3BA-3D1A07F52CDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="260">
   <si>
     <t>губ</t>
   </si>
@@ -929,7 +929,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1011,10 +1011,13 @@
     <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="3" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1276,23 +1279,23 @@
         <v>246</v>
       </c>
       <c r="G1" s="28"/>
-      <c r="H1" s="31" t="s">
+      <c r="H1" s="32" t="s">
         <v>237</v>
       </c>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31"/>
-      <c r="N1" s="31"/>
-      <c r="O1" s="31"/>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="31"/>
-      <c r="R1" s="31"/>
-      <c r="S1" s="31"/>
-      <c r="T1" s="31"/>
-      <c r="U1" s="31"/>
-      <c r="V1" s="31"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="32"/>
+      <c r="R1" s="32"/>
+      <c r="S1" s="32"/>
+      <c r="T1" s="32"/>
+      <c r="U1" s="32"/>
+      <c r="V1" s="32"/>
       <c r="X1" s="29" t="s">
         <v>241</v>
       </c>
@@ -1699,14 +1702,22 @@
       <c r="A8" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="B8" s="32">
+      <c r="B8" s="31">
         <f>SUM(H8:I8)</f>
         <v>355046</v>
       </c>
-      <c r="C8" s="32"/>
-      <c r="D8" s="32"/>
-      <c r="E8" s="19"/>
-      <c r="F8" s="19"/>
+      <c r="C8" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>4</v>
+      </c>
       <c r="G8" s="9"/>
       <c r="H8" s="6">
         <v>138046</v>
@@ -2450,10 +2461,10 @@
       <c r="D20" s="5">
         <v>37791</v>
       </c>
-      <c r="E20" s="22">
+      <c r="E20" s="33">
         <v>42.3</v>
       </c>
-      <c r="F20" s="22">
+      <c r="F20" s="33">
         <v>28.4</v>
       </c>
       <c r="G20" s="10"/>

--- a/rtss-pre1917/src/main/resources/ugvi/year-volumes/new/1888-new.xlsx
+++ b/rtss-pre1917/src/main/resources/ugvi/year-volumes/new/1888-new.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\ugvi\year-volumes\new\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{464B532B-9910-4F1C-A3BA-3D1A07F52CDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C67D880-6A9F-45A7-A562-6C2A1518F0D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="260">
   <si>
     <t>губ</t>
   </si>
@@ -929,7 +929,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1016,9 +1016,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1743,8 +1740,12 @@
         <f>SUM(H8:V8)</f>
         <v>355046</v>
       </c>
-      <c r="Y8" s="4"/>
-      <c r="Z8" s="4"/>
+      <c r="Y8" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z8" s="12" t="s">
+        <v>4</v>
+      </c>
       <c r="AA8" s="4"/>
       <c r="AB8" s="4"/>
       <c r="AC8" s="4"/>
@@ -2461,10 +2462,10 @@
       <c r="D20" s="5">
         <v>37791</v>
       </c>
-      <c r="E20" s="33">
+      <c r="E20" s="19">
         <v>42.3</v>
       </c>
-      <c r="F20" s="33">
+      <c r="F20" s="19">
         <v>28.4</v>
       </c>
       <c r="G20" s="10"/>

--- a/rtss-pre1917/src/main/resources/ugvi/year-volumes/new/1888-new.xlsx
+++ b/rtss-pre1917/src/main/resources/ugvi/year-volumes/new/1888-new.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\ugvi\year-volumes\new\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BA30AAF-15F5-4AE1-A4A6-A5FFC3B7EF02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9705BC14-0E6F-413A-B4E7-BC165E7489B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1254,9 +1254,9 @@
     <col min="28" max="28" width="9.38671875" bestFit="1" customWidth="1"/>
     <col min="29" max="30" width="7.83203125" bestFit="1" customWidth="1"/>
     <col min="31" max="31" width="5.38671875" customWidth="1"/>
-    <col min="32" max="33" width="4.38671875" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="4.38671875" customWidth="1"/>
     <col min="34" max="34" width="2.27734375" customWidth="1"/>
-    <col min="35" max="36" width="4.94140625" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="4.94140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.4">
@@ -14789,29 +14789,33 @@
         <v>4</v>
       </c>
       <c r="G200" s="10"/>
-      <c r="H200" s="9"/>
-      <c r="I200" s="9"/>
-      <c r="J200" s="9"/>
-      <c r="K200" s="9"/>
-      <c r="L200" s="9"/>
-      <c r="M200" s="9"/>
-      <c r="N200" s="9"/>
-      <c r="O200" s="9"/>
-      <c r="P200" s="9"/>
-      <c r="Q200" s="9"/>
-      <c r="R200" s="9"/>
-      <c r="S200" s="9"/>
-      <c r="T200" s="9"/>
-      <c r="U200" s="9"/>
-      <c r="V200" s="9"/>
+      <c r="H200" s="7"/>
+      <c r="I200" s="7"/>
+      <c r="J200" s="7"/>
+      <c r="K200" s="7"/>
+      <c r="L200" s="7"/>
+      <c r="M200" s="7"/>
+      <c r="N200" s="7"/>
+      <c r="O200" s="7"/>
+      <c r="P200" s="7"/>
+      <c r="Q200" s="7"/>
+      <c r="R200" s="7"/>
+      <c r="S200" s="7"/>
+      <c r="T200" s="7"/>
+      <c r="U200" s="7"/>
+      <c r="V200" s="7"/>
       <c r="W200" s="3"/>
-      <c r="X200" s="3"/>
-      <c r="Y200" s="3"/>
-      <c r="Z200" s="3"/>
-      <c r="AA200" s="3"/>
-      <c r="AB200" s="3"/>
-      <c r="AC200" s="3"/>
-      <c r="AD200" s="3"/>
+      <c r="X200" s="4"/>
+      <c r="Y200" s="4"/>
+      <c r="Z200" s="4"/>
+      <c r="AA200" s="4"/>
+      <c r="AB200" s="4"/>
+      <c r="AC200" s="4"/>
+      <c r="AD200" s="4"/>
+      <c r="AF200" s="18"/>
+      <c r="AG200" s="18"/>
+      <c r="AI200" s="18"/>
+      <c r="AJ200" s="18"/>
     </row>
     <row r="201" spans="1:36" ht="14.4" x14ac:dyDescent="0.4">
       <c r="A201" s="1" t="s">
@@ -14833,29 +14837,45 @@
         <v>39.1</v>
       </c>
       <c r="G201" s="10"/>
-      <c r="H201" s="9"/>
-      <c r="I201" s="9"/>
-      <c r="J201" s="9"/>
-      <c r="K201" s="9"/>
-      <c r="L201" s="9"/>
-      <c r="M201" s="9"/>
-      <c r="N201" s="9"/>
-      <c r="O201" s="9"/>
-      <c r="P201" s="9"/>
-      <c r="Q201" s="9"/>
-      <c r="R201" s="9"/>
-      <c r="S201" s="9"/>
-      <c r="T201" s="9"/>
-      <c r="U201" s="9"/>
-      <c r="V201" s="9"/>
+      <c r="H201" s="7"/>
+      <c r="I201" s="7"/>
+      <c r="J201" s="7"/>
+      <c r="K201" s="7"/>
+      <c r="L201" s="7"/>
+      <c r="M201" s="7"/>
+      <c r="N201" s="7"/>
+      <c r="O201" s="7"/>
+      <c r="P201" s="7"/>
+      <c r="Q201" s="7"/>
+      <c r="R201" s="7"/>
+      <c r="S201" s="7"/>
+      <c r="T201" s="7"/>
+      <c r="U201" s="7"/>
+      <c r="V201" s="7"/>
       <c r="W201" s="3"/>
-      <c r="X201" s="3"/>
-      <c r="Y201" s="3"/>
-      <c r="Z201" s="3"/>
-      <c r="AA201" s="3"/>
-      <c r="AB201" s="3"/>
-      <c r="AC201" s="3"/>
-      <c r="AD201" s="3"/>
+      <c r="X201" s="4"/>
+      <c r="Y201" s="4"/>
+      <c r="Z201" s="4"/>
+      <c r="AA201" s="4"/>
+      <c r="AB201" s="4"/>
+      <c r="AC201" s="4"/>
+      <c r="AD201" s="4"/>
+      <c r="AF201" s="18">
+        <f>C201/B201*1000</f>
+        <v>61.696050676491453</v>
+      </c>
+      <c r="AG201" s="18">
+        <f>D201/B201*1000</f>
+        <v>39.142878729295276</v>
+      </c>
+      <c r="AI201" s="18">
+        <f>AF201-E201</f>
+        <v>9.605067649145127E-2</v>
+      </c>
+      <c r="AJ201" s="18">
+        <f>AG201-F201</f>
+        <v>4.2878729295274809E-2</v>
+      </c>
     </row>
     <row r="202" spans="1:36" ht="14.4" x14ac:dyDescent="0.4">
       <c r="A202" s="1" t="s">
